--- a/Siber_Guvence_Linux_Server_Baseline_Guncellenmis.xlsx
+++ b/Siber_Guvence_Linux_Server_Baseline_Guncellenmis.xlsx
@@ -727,7 +727,7 @@
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>minlen=14, dcredit=-1, ucredit=-1, lcredit=-1, ocredit=-1, SHA512 algoritması. Root parolası asla e-posta/sohbet üzerinden paylaşılmamalıdır.</t>
+          <t>minlen=21, dcredit=-1, ucredit=-1, lcredit=-1, ocredit=-1, SHA512 algoritması. Root parolası asla e-posta/sohbet üzerinden paylaşılmamalıdır.</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
